--- a/inst/resources/outputs_schema_data_analytics_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_template.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>base</t>
         </is>
       </c>
     </row>
